--- a/artfynd/A 23200-2026 artfynd.xlsx
+++ b/artfynd/A 23200-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80069186</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417574.2209305586</v>
+        <v>417574</v>
       </c>
       <c r="R2" t="n">
-        <v>6286807.01092758</v>
+        <v>6286807</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88425920</v>
+        <v>88426020</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,26 +798,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -856,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417555.7547605825</v>
+        <v>417556</v>
       </c>
       <c r="R3" t="n">
-        <v>6286762.915479405</v>
+        <v>6286763</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,19 +869,9 @@
           <t>2019-07-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88426020</v>
+        <v>88425920</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,26 +909,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417555.7547605825</v>
+        <v>417556</v>
       </c>
       <c r="R4" t="n">
-        <v>6286762.915479405</v>
+        <v>6286763</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,19 +980,9 @@
           <t>2019-07-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 23200-2026 artfynd.xlsx
+++ b/artfynd/A 23200-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80069186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88426020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,8 +1021,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88425920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>